--- a/inputs/AddictO_Human-being_Defs.xlsx
+++ b/inputs/AddictO_Human-being_Defs.xlsx
@@ -3579,59 +3579,59 @@
       <c r="U54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001048</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>alcohol use disorder</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of alcohol.</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q55" s="3" t="inlineStr"/>
-      <c r="R55" s="3" t="inlineStr"/>
-      <c r="S55" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="3" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr"/>
+      <c r="R55" s="7" t="inlineStr"/>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T55" s="7" t="inlineStr"/>
+      <c r="U55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -4383,63 +4383,63 @@
       <c r="U70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001053</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>amphetamine use disorder</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of amphetamine.</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q71" s="3" t="inlineStr"/>
-      <c r="R71" s="3" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr"/>
+      <c r="R71" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="3" t="inlineStr"/>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T71" s="7" t="inlineStr"/>
+      <c r="U71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -6935,56 +6935,67 @@
       <c r="U121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001058</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>cannabis use disorder</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of cannabis.</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
+      <c r="G122" s="7" t="n"/>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="n"/>
+      <c r="J122" s="7" t="n"/>
+      <c r="K122" s="7" t="inlineStr">
         <is>
           <t>CUD</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
+      <c r="L122" s="7" t="n"/>
+      <c r="M122" s="7" t="n"/>
+      <c r="N122" s="7" t="n"/>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P122" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q122" s="7" t="n"/>
+      <c r="R122" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="S122" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T122" s="7" t="n"/>
+      <c r="U122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -9052,63 +9063,63 @@
       <c r="U164" s="7" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001061</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>cocaine use disorder</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of cocaine.</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr"/>
-      <c r="E165" s="3" t="inlineStr"/>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="D165" s="7" t="inlineStr"/>
+      <c r="E165" s="7" t="inlineStr"/>
+      <c r="F165" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr"/>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr"/>
-      <c r="J165" s="3" t="inlineStr"/>
-      <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr"/>
-      <c r="M165" s="3" t="inlineStr"/>
-      <c r="N165" s="3" t="inlineStr"/>
-      <c r="O165" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P165" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q165" s="3" t="inlineStr"/>
-      <c r="R165" s="3" t="inlineStr">
+      <c r="G165" s="7" t="inlineStr"/>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr"/>
+      <c r="K165" s="7" t="inlineStr"/>
+      <c r="L165" s="7" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+      <c r="N165" s="7" t="inlineStr"/>
+      <c r="O165" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P165" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q165" s="7" t="inlineStr"/>
+      <c r="R165" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S165" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T165" s="3" t="inlineStr"/>
-      <c r="U165" s="3" t="inlineStr"/>
+      <c r="S165" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T165" s="7" t="inlineStr"/>
+      <c r="U165" s="7" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -23716,63 +23727,63 @@
       <c r="U453" s="7" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="3" t="inlineStr">
+      <c r="A454" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001071</t>
         </is>
       </c>
-      <c r="B454" s="3" t="inlineStr">
+      <c r="B454" s="7" t="inlineStr">
         <is>
           <t>opioid use disorder</t>
         </is>
       </c>
-      <c r="C454" s="3" t="inlineStr">
+      <c r="C454" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of a opioids</t>
         </is>
       </c>
-      <c r="D454" s="3" t="inlineStr"/>
-      <c r="E454" s="3" t="inlineStr"/>
-      <c r="F454" s="3" t="inlineStr">
+      <c r="D454" s="7" t="inlineStr"/>
+      <c r="E454" s="7" t="inlineStr"/>
+      <c r="F454" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="G454" s="3" t="inlineStr"/>
-      <c r="H454" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I454" s="3" t="inlineStr"/>
-      <c r="J454" s="3" t="inlineStr"/>
-      <c r="K454" s="3" t="inlineStr"/>
-      <c r="L454" s="3" t="inlineStr"/>
-      <c r="M454" s="3" t="inlineStr"/>
-      <c r="N454" s="3" t="inlineStr"/>
-      <c r="O454" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P454" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q454" s="3" t="inlineStr"/>
-      <c r="R454" s="3" t="inlineStr">
+      <c r="G454" s="7" t="inlineStr"/>
+      <c r="H454" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I454" s="7" t="inlineStr"/>
+      <c r="J454" s="7" t="inlineStr"/>
+      <c r="K454" s="7" t="inlineStr"/>
+      <c r="L454" s="7" t="inlineStr"/>
+      <c r="M454" s="7" t="inlineStr"/>
+      <c r="N454" s="7" t="inlineStr"/>
+      <c r="O454" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P454" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q454" s="7" t="inlineStr"/>
+      <c r="R454" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S454" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T454" s="3" t="inlineStr"/>
-      <c r="U454" s="3" t="inlineStr"/>
+      <c r="S454" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T454" s="7" t="inlineStr"/>
+      <c r="U454" s="7" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -35943,63 +35954,63 @@
       <c r="U696" s="4" t="inlineStr"/>
     </row>
     <row r="697">
-      <c r="A697" s="2" t="inlineStr">
+      <c r="A697" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001228</t>
         </is>
       </c>
-      <c r="B697" s="2" t="inlineStr">
+      <c r="B697" s="7" t="inlineStr">
         <is>
           <t>substance misuse</t>
         </is>
       </c>
-      <c r="C697" s="2" t="inlineStr">
+      <c r="C697" s="7" t="inlineStr">
         <is>
           <t>Substance use that is outside of the terms approved or recommended by the jurisdiction in which the behaviour occurs.</t>
         </is>
       </c>
-      <c r="D697" s="2" t="inlineStr"/>
-      <c r="E697" s="2" t="inlineStr"/>
-      <c r="F697" s="2" t="inlineStr">
+      <c r="D697" s="7" t="inlineStr"/>
+      <c r="E697" s="7" t="inlineStr"/>
+      <c r="F697" s="7" t="inlineStr">
         <is>
           <t>substance use</t>
         </is>
       </c>
-      <c r="G697" s="2" t="inlineStr"/>
-      <c r="H697" s="2" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I697" s="2" t="inlineStr"/>
-      <c r="J697" s="2" t="inlineStr"/>
-      <c r="K697" s="2" t="inlineStr"/>
-      <c r="L697" s="2" t="inlineStr"/>
-      <c r="M697" s="2" t="inlineStr"/>
-      <c r="N697" s="2" t="inlineStr"/>
-      <c r="O697" s="2" t="inlineStr">
+      <c r="G697" s="7" t="inlineStr"/>
+      <c r="H697" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I697" s="7" t="inlineStr"/>
+      <c r="J697" s="7" t="inlineStr"/>
+      <c r="K697" s="7" t="inlineStr"/>
+      <c r="L697" s="7" t="inlineStr"/>
+      <c r="M697" s="7" t="inlineStr"/>
+      <c r="N697" s="7" t="inlineStr"/>
+      <c r="O697" s="7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="P697" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q697" s="2" t="inlineStr"/>
-      <c r="R697" s="2" t="inlineStr">
+      <c r="P697" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q697" s="7" t="inlineStr"/>
+      <c r="R697" s="7" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="S697" s="2" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T697" s="2" t="inlineStr"/>
-      <c r="U697" s="2" t="inlineStr"/>
+      <c r="S697" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T697" s="7" t="inlineStr"/>
+      <c r="U697" s="7" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="7" t="inlineStr">
@@ -36065,71 +36076,71 @@
       <c r="U698" s="7" t="inlineStr"/>
     </row>
     <row r="699">
-      <c r="A699" s="3" t="inlineStr">
+      <c r="A699" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000401</t>
         </is>
       </c>
-      <c r="B699" s="3" t="inlineStr">
+      <c r="B699" s="7" t="inlineStr">
         <is>
           <t>substance use disorder</t>
         </is>
       </c>
-      <c r="C699" s="3" t="inlineStr">
+      <c r="C699" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder in which the behaviour that is the subject of the addiction is use of a psychoactive substance.</t>
         </is>
       </c>
-      <c r="D699" s="3" t="inlineStr"/>
-      <c r="E699" s="3" t="inlineStr"/>
-      <c r="F699" s="3" t="inlineStr">
+      <c r="D699" s="7" t="inlineStr"/>
+      <c r="E699" s="7" t="inlineStr"/>
+      <c r="F699" s="7" t="inlineStr">
         <is>
           <t>addictive disorder</t>
         </is>
       </c>
-      <c r="G699" s="3" t="inlineStr">
+      <c r="G699" s="7" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="H699" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I699" s="3" t="inlineStr"/>
-      <c r="J699" s="3" t="inlineStr"/>
-      <c r="K699" s="3" t="inlineStr">
+      <c r="H699" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I699" s="7" t="inlineStr"/>
+      <c r="J699" s="7" t="inlineStr"/>
+      <c r="K699" s="7" t="inlineStr">
         <is>
           <t>drug use disorder</t>
         </is>
       </c>
-      <c r="L699" s="3" t="inlineStr"/>
-      <c r="M699" s="3" t="inlineStr"/>
-      <c r="N699" s="3" t="inlineStr"/>
-      <c r="O699" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P699" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q699" s="3" t="inlineStr"/>
-      <c r="R699" s="3" t="inlineStr">
+      <c r="L699" s="7" t="inlineStr"/>
+      <c r="M699" s="7" t="inlineStr"/>
+      <c r="N699" s="7" t="inlineStr"/>
+      <c r="O699" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P699" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q699" s="7" t="inlineStr"/>
+      <c r="R699" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S699" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T699" s="3" t="inlineStr"/>
-      <c r="U699" s="3" t="inlineStr"/>
+      <c r="S699" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T699" s="7" t="inlineStr"/>
+      <c r="U699" s="7" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="7" t="inlineStr"/>

--- a/inputs/AddictO_Human-being_Defs.xlsx
+++ b/inputs/AddictO_Human-being_Defs.xlsx
@@ -32417,69 +32417,69 @@
       <c r="U626" s="7" t="inlineStr"/>
     </row>
     <row r="627">
-      <c r="A627" s="3" t="inlineStr">
+      <c r="A627" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001034</t>
         </is>
       </c>
-      <c r="B627" s="3" t="inlineStr">
+      <c r="B627" s="7" t="inlineStr">
         <is>
           <t>severe alcohol use disorder</t>
         </is>
       </c>
-      <c r="C627" s="3" t="inlineStr">
+      <c r="C627" s="7" t="inlineStr">
         <is>
           <t>Alcohol use disorder which is characterised by impairments and/or problems which are extreme in nature.</t>
         </is>
       </c>
-      <c r="D627" s="3" t="inlineStr"/>
-      <c r="E627" s="3" t="inlineStr"/>
-      <c r="F627" s="3" t="inlineStr">
+      <c r="D627" s="7" t="inlineStr"/>
+      <c r="E627" s="7" t="inlineStr"/>
+      <c r="F627" s="7" t="inlineStr">
         <is>
           <t>alcohol use disorder</t>
         </is>
       </c>
-      <c r="G627" s="3" t="inlineStr"/>
-      <c r="H627" s="3" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I627" s="3" t="inlineStr"/>
-      <c r="J627" s="3" t="inlineStr"/>
-      <c r="K627" s="3" t="inlineStr"/>
-      <c r="L627" s="3" t="inlineStr"/>
-      <c r="M627" s="3" t="inlineStr">
+      <c r="G627" s="7" t="inlineStr"/>
+      <c r="H627" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I627" s="7" t="inlineStr"/>
+      <c r="J627" s="7" t="inlineStr"/>
+      <c r="K627" s="7" t="inlineStr"/>
+      <c r="L627" s="7" t="inlineStr"/>
+      <c r="M627" s="7" t="inlineStr">
         <is>
           <t>Give indication of severity and how this is operationalised.</t>
         </is>
       </c>
-      <c r="N627" s="3" t="inlineStr"/>
-      <c r="O627" s="3" t="inlineStr">
+      <c r="N627" s="7" t="inlineStr"/>
+      <c r="O627" s="7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P627" s="3" t="n">
+      <c r="P627" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q627" s="3" t="inlineStr">
+      <c r="Q627" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">extent of severity is subjective and how this is operationalised needs to be indicated </t>
         </is>
       </c>
-      <c r="R627" s="3" t="inlineStr">
+      <c r="R627" s="7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="S627" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T627" s="3" t="inlineStr"/>
-      <c r="U627" s="3" t="inlineStr"/>
+      <c r="S627" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T627" s="7" t="inlineStr"/>
+      <c r="U627" s="7" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="7" t="inlineStr"/>
@@ -37284,67 +37284,67 @@
       <c r="U720" s="7" t="inlineStr"/>
     </row>
     <row r="721">
-      <c r="A721" s="5" t="inlineStr">
+      <c r="A721" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001074</t>
         </is>
       </c>
-      <c r="B721" s="5" t="inlineStr">
+      <c r="B721" s="7" t="inlineStr">
         <is>
           <t>tobacco use disorder</t>
         </is>
       </c>
-      <c r="C721" s="5" t="inlineStr">
+      <c r="C721" s="7" t="inlineStr">
         <is>
           <t>An addictive disorder that involves addiction to tobacco use.</t>
         </is>
       </c>
-      <c r="D721" s="5" t="inlineStr"/>
-      <c r="E721" s="5" t="inlineStr"/>
-      <c r="F721" s="5" t="inlineStr">
+      <c r="D721" s="7" t="inlineStr"/>
+      <c r="E721" s="7" t="inlineStr"/>
+      <c r="F721" s="7" t="inlineStr">
         <is>
           <t>substance use disorder</t>
         </is>
       </c>
-      <c r="G721" s="5" t="inlineStr">
+      <c r="G721" s="7" t="inlineStr">
         <is>
           <t>disposition</t>
         </is>
       </c>
-      <c r="H721" s="5" t="inlineStr">
-        <is>
-          <t>Human being</t>
-        </is>
-      </c>
-      <c r="I721" s="5" t="inlineStr"/>
-      <c r="J721" s="5" t="inlineStr"/>
-      <c r="K721" s="5" t="inlineStr"/>
-      <c r="L721" s="5" t="inlineStr"/>
-      <c r="M721" s="5" t="inlineStr"/>
-      <c r="N721" s="5" t="inlineStr"/>
-      <c r="O721" s="5" t="inlineStr">
+      <c r="H721" s="7" t="inlineStr">
+        <is>
+          <t>Human being</t>
+        </is>
+      </c>
+      <c r="I721" s="7" t="inlineStr"/>
+      <c r="J721" s="7" t="inlineStr"/>
+      <c r="K721" s="7" t="inlineStr"/>
+      <c r="L721" s="7" t="inlineStr"/>
+      <c r="M721" s="7" t="inlineStr"/>
+      <c r="N721" s="7" t="inlineStr"/>
+      <c r="O721" s="7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="P721" s="5" t="inlineStr">
+      <c r="P721" s="7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="Q721" s="5" t="inlineStr"/>
-      <c r="R721" s="5" t="inlineStr">
+      <c r="Q721" s="7" t="inlineStr"/>
+      <c r="R721" s="7" t="inlineStr">
         <is>
           <t>KS; RW</t>
         </is>
       </c>
-      <c r="S721" s="5" t="inlineStr">
-        <is>
-          <t>To Be Discussed</t>
-        </is>
-      </c>
-      <c r="T721" s="5" t="inlineStr"/>
-      <c r="U721" s="5" t="inlineStr"/>
+      <c r="S721" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T721" s="7" t="inlineStr"/>
+      <c r="U721" s="7" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
